--- a/results/Int Task Remove ACC -0.9/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_6_permute.xlsx
@@ -440,657 +440,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6033571844745433</v>
+        <v>0.6024014095186406</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6204715422496428</v>
+        <v>0.6024014095186406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6269584407499341</v>
+        <v>0.6024014095186406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6192775219289495</v>
+        <v>0.6064212513269109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6249283667621777</v>
+        <v>0.6099628065862671</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6209492301921127</v>
+        <v>0.6109175838647629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6390564765226553</v>
+        <v>0.6060225794350751</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6403299119649456</v>
+        <v>0.5965508296685317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6347983893495941</v>
+        <v>0.5941629885626262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6324502558044871</v>
+        <v>0.6008897287115595</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6331665881827107</v>
+        <v>0.6028397889712749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6324893647588414</v>
+        <v>0.6024419152213647</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6320515839126514</v>
+        <v>0.602004333910656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6271162733157211</v>
+        <v>0.6005714696187276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6081326671508728</v>
+        <v>0.595955814862999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6205088553846645</v>
+        <v>0.5943244127670783</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6220608423589883</v>
+        <v>0.5980663016497594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6197530149811239</v>
+        <v>0.5751847698557757</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6263586370928478</v>
+        <v>0.5805967707177691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6255628895930274</v>
+        <v>0.5806763853748473</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6429156922683992</v>
+        <v>0.5807957075927241</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6355137240504106</v>
+        <v>0.5778509629582332</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6352748800791757</v>
+        <v>0.5879193238141607</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6329267465340687</v>
+        <v>0.5967539567885961</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5916189111747852</v>
+        <v>0.5974702891668197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5781289158838225</v>
+        <v>0.6069432361462515</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5560417348412895</v>
+        <v>0.6179264671843947</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5512275422815686</v>
+        <v>0.607383211882737</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5445812149316391</v>
+        <v>0.6020109185815422</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5193110438898245</v>
+        <v>0.6131160657988204</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5280263546463833</v>
+        <v>0.6029688884277402</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5328423430254368</v>
+        <v>0.584385550438579</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5344741441923202</v>
+        <v>0.5862565946476603</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5478823299359092</v>
+        <v>0.5820773239897519</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5556827705102522</v>
+        <v>0.57483458508592</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5588266515551795</v>
+        <v>0.5536614760836771</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5588266515551795</v>
+        <v>0.5483687974395608</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5588266515551795</v>
+        <v>0.5702193294011542</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.553453959183022</v>
+        <v>0.5330177347135868</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.600215897390874</v>
+        <v>0.5389471310788485</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6000568676121988</v>
+        <v>0.5389471310788485</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5997783160801653</v>
+        <v>0.5612304554995969</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5993425305887893</v>
+        <v>0.5785010495566322</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5852561237439241</v>
+        <v>0.5775061656463752</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5450688796481791</v>
+        <v>0.5843105250975729</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5465011453336632</v>
+        <v>0.5601956644930601</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5452674174521713</v>
+        <v>0.5506079846118237</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5366720275199336</v>
+        <v>0.5412174457862098</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5441063204859088</v>
+        <v>0.5377547070420061</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5516292072056254</v>
+        <v>0.5423306542369364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5527833204300389</v>
+        <v>0.5195311315258079</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5527833204300389</v>
+        <v>0.5189341213654612</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5351956644930601</v>
+        <v>0.5094605757795851</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5506337246889241</v>
+        <v>0.5201642576082879</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5448633581023378</v>
+        <v>0.498278008795524</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5797281927672379</v>
+        <v>0.4958502605933387</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6210723435841361</v>
+        <v>0.5061586626333895</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6151834529215985</v>
+        <v>0.5040100645696818</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6149446089503636</v>
+        <v>0.5034527619701336</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5968377616907838</v>
+        <v>0.5097393268470999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5528635336935614</v>
+        <v>0.5062380777549864</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.516413988235388</v>
+        <v>0.5067532783679594</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4818765912954641</v>
+        <v>0.4955258159005834</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5015344278519607</v>
+        <v>0.5122005970101603</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5088960899027065</v>
+        <v>0.5125190556384736</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4713720458771979</v>
+        <v>0.5125190556384736</v>
       </c>
     </row>
     <row r="68">
@@ -1100,57 +1100,57 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4997416015515879</v>
+        <v>0.5222272549504753</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5184480529327725</v>
+        <v>0.5188459266826827</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5186862982975633</v>
+        <v>0.5246166923402319</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5523064306294945</v>
+        <v>0.527442114756846</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5505555067802157</v>
+        <v>0.5262482939716341</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.551828942222506</v>
+        <v>0.5679891213255541</v>
       </c>
     </row>
     <row r="74">
@@ -1160,167 +1160,167 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5636871363465852</v>
+        <v>0.5493654771691503</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5636871363465852</v>
+        <v>0.5253334237894183</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5570847068025637</v>
+        <v>0.5258901277825223</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5580398831520221</v>
+        <v>0.5834297754826763</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5681477520332665</v>
+        <v>0.6148645952223224</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5575661859191802</v>
+        <v>0.6221093294809683</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5536724505351542</v>
+        <v>0.5989598215354655</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5417749479212394</v>
+        <v>0.5231983941384457</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5514053283954953</v>
+        <v>0.5231983941384457</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5451592692212529</v>
+        <v>0.5229198426064123</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5465917344422185</v>
+        <v>0.5343005483235029</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5423352435530086</v>
+        <v>0.5292469131861027</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5423352435530086</v>
+        <v>0.5285704879041591</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5100266579403149</v>
+        <v>0.5144044664022157</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5092698198593674</v>
+        <v>0.5023475349386628</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5103844250584639</v>
+        <v>0.5033422193134384</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4970542576881021</v>
+        <v>0.5002785515320334</v>
       </c>
     </row>
   </sheetData>
